--- a/output/2026-10-03_02_Malesia_Pahang_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-03_02_Malesia_Pahang_Utensilerie_e_Macchine_Utensili.xlsx
@@ -493,8 +493,6 @@
           <t>Utensilerie e Macchine Utensili</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>Distributore B2B di utensili, ferramenta, power tools ed elettrico; verificato tramite profilo su marketplace Lapasar Mall (SSM CA0203857H/201303295436); indirizzo B116 Perkampungan Setali, Jalan Haji Ahmad, 25300 Kuantan</t>
@@ -502,7 +500,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>
@@ -586,7 +584,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (03/10/2026)</t>
         </is>
       </c>
     </row>

--- a/output/2026-10-03_02_Malesia_Pahang_Utensilerie_e_Macchine_Utensili.xlsx
+++ b/output/2026-10-03_02_Malesia_Pahang_Utensilerie_e_Macchine_Utensili.xlsx
@@ -537,7 +537,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore di compressori d'aria e sistemi di trattamento aria industriale dal 1979 (43 anni di attivita); 5 filiali in Malesia; verificato tramite sito ufficiale aziendale</t>
+          <t>Distributore di compressori d'aria e sistemi di trattamento aria industriale dal 1979 (43 anni di attivita); 5 filiali in Malesia; verificato tramite sito ufficiale aziendale [DUPLICATO — vedi anche: 2026-10-02_21_Malesia_Pahang_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Marketplace B2B multi-categoria (tools &amp; hardware, MRO industrial, safety) con oltre 10.000 fornitori; sede fuori Pahang ma presenza logistico-commerciale comprovata su Kuantan; incluso come partner commerciale regionale in assenza di distributori locali di aspiratori industriali con sede in Pahang</t>
+          <t>Marketplace B2B multi-categoria (tools &amp; hardware, MRO industrial, safety) con oltre 10.000 fornitori; sede fuori Pahang ma presenza logistico-commerciale comprovata su Kuantan; incluso come partner commerciale regionale in assenza di distributori locali di aspiratori industriali con sede in Pahang [DUPLICATO — vedi anche: 2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
